--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MEGACALZADO ARDOI.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MEGACALZADO ARDOI.xlsx
@@ -565,13 +565,13 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>52.9189</v>
+        <v>57.2855</v>
       </c>
       <c r="E2" t="n">
-        <v>51.602</v>
+        <v>55.0601</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3171</v>
+        <v>2.2252</v>
       </c>
       <c r="G2" t="n">
         <v>29.2749</v>
@@ -610,13 +610,13 @@
         <v>37.4435</v>
       </c>
       <c r="S2" t="n">
-        <v>-9.294599999999999</v>
+        <v>-4.9283</v>
       </c>
       <c r="T2" t="n">
-        <v>-8.321300000000001</v>
+        <v>-4.863</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9733999999999998</v>
+        <v>-0.06530000000000002</v>
       </c>
       <c r="V2" t="n">
         <v>20.2004</v>
@@ -643,13 +643,13 @@
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>13.4266</v>
+        <v>6.965299999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>15.443</v>
+        <v>8.7681</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.015899999999999</v>
+        <v>-1.8027</v>
       </c>
       <c r="G3" t="n">
         <v>6.627900000000002</v>
@@ -688,13 +688,13 @@
         <v>26.249</v>
       </c>
       <c r="S3" t="n">
-        <v>5.9721</v>
+        <v>-0.4894999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>5.908399999999999</v>
+        <v>-0.7663</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06380000000000008</v>
+        <v>0.2769</v>
       </c>
       <c r="V3" t="n">
         <v>5.072900000000001</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ARRIAZU ARBIZU</t>
+          <t>M. ARIZTIMUÑO MORRAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>6.188</v>
+        <v>2.361200000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>4.910299999999999</v>
+        <v>8.817799999999998</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2776</v>
+        <v>-6.456300000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9650000000000007</v>
+        <v>-18.7208</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9356</v>
+        <v>-14.3503</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.9006</v>
+        <v>-4.3704</v>
       </c>
       <c r="J4" t="n">
-        <v>11.6133</v>
+        <v>18.9329</v>
       </c>
       <c r="K4" t="n">
-        <v>10.5965</v>
+        <v>5.3529</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0169</v>
+        <v>13.5806</v>
       </c>
       <c r="M4" t="n">
-        <v>-12.5785</v>
+        <v>-37.6537</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.6608</v>
+        <v>-19.7031</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.9175</v>
+        <v>-17.9508</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7722</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q4" t="n">
-        <v>-12.9315</v>
+        <v>-47.6729</v>
       </c>
       <c r="R4" t="n">
-        <v>13.7035</v>
+        <v>45.5501</v>
       </c>
       <c r="S4" t="n">
-        <v>4.7042</v>
+        <v>-4.3708</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5436000000000001</v>
+        <v>-3.1565</v>
       </c>
       <c r="U4" t="n">
-        <v>4.160600000000001</v>
+        <v>-1.2142</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6769</v>
+        <v>27.576</v>
       </c>
       <c r="W4" t="n">
-        <v>5.6851</v>
+        <v>40.7145</v>
       </c>
       <c r="X4" t="n">
-        <v>-4.0083</v>
+        <v>-13.1386</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ARIZTIMUÑO MORRAS</t>
+          <t>J. ARRIAZU ARBIZU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>3.285800000000001</v>
+        <v>1.1816</v>
       </c>
       <c r="E5" t="n">
-        <v>9.606</v>
+        <v>1.9653</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.320099999999999</v>
+        <v>-0.7842</v>
       </c>
       <c r="G5" t="n">
-        <v>-18.7208</v>
+        <v>-0.9650000000000007</v>
       </c>
       <c r="H5" t="n">
-        <v>-14.3503</v>
+        <v>2.9356</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.3704</v>
+        <v>-3.9006</v>
       </c>
       <c r="J5" t="n">
-        <v>18.9329</v>
+        <v>11.6133</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3529</v>
+        <v>10.5965</v>
       </c>
       <c r="L5" t="n">
-        <v>13.5806</v>
+        <v>1.0169</v>
       </c>
       <c r="M5" t="n">
-        <v>-37.6537</v>
+        <v>-12.5785</v>
       </c>
       <c r="N5" t="n">
-        <v>-19.7031</v>
+        <v>-7.6608</v>
       </c>
       <c r="O5" t="n">
-        <v>-17.9508</v>
+        <v>-4.9175</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.1231</v>
+        <v>0.7722</v>
       </c>
       <c r="Q5" t="n">
-        <v>-47.6729</v>
+        <v>-12.9315</v>
       </c>
       <c r="R5" t="n">
-        <v>45.5501</v>
+        <v>13.7035</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.446300000000001</v>
+        <v>-0.3023999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.3682</v>
+        <v>-2.4013</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0781</v>
+        <v>2.0987</v>
       </c>
       <c r="V5" t="n">
-        <v>27.576</v>
+        <v>1.6769</v>
       </c>
       <c r="W5" t="n">
-        <v>40.7145</v>
+        <v>5.6851</v>
       </c>
       <c r="X5" t="n">
-        <v>-13.1386</v>
+        <v>-4.0083</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. OREJA ELSO</t>
+          <t>M. BIDAURRE SOLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>-8.8453</v>
+        <v>-0.9917000000000007</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.535200000000001</v>
+        <v>-4.045500000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.31</v>
+        <v>3.053100000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.5741</v>
+        <v>16.7691</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.5703</v>
+        <v>5.8578</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9959999999999996</v>
+        <v>10.9118</v>
       </c>
       <c r="J6" t="n">
-        <v>10.5382</v>
+        <v>38.9392</v>
       </c>
       <c r="K6" t="n">
-        <v>5.966299999999999</v>
+        <v>21.1218</v>
       </c>
       <c r="L6" t="n">
-        <v>4.5722</v>
+        <v>17.8174</v>
       </c>
       <c r="M6" t="n">
-        <v>-13.1123</v>
+        <v>-22.1701</v>
       </c>
       <c r="N6" t="n">
-        <v>-9.536300000000001</v>
+        <v>-15.2642</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.576</v>
+        <v>-6.9057</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8951</v>
+        <v>8.106199999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-12.1595</v>
+        <v>-41.4964</v>
       </c>
       <c r="R6" t="n">
-        <v>15.0546</v>
+        <v>49.6031</v>
       </c>
       <c r="S6" t="n">
-        <v>-6.6278</v>
+        <v>-14.9447</v>
       </c>
       <c r="T6" t="n">
-        <v>-4.1575</v>
+        <v>-8.644500000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.4701</v>
+        <v>-6.3003</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.5385</v>
+        <v>-10.9231</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2437</v>
+        <v>7.1567</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7822</v>
+        <v>-18.0798</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MENDIVIL ODERIZ</t>
+          <t>H. OREJA ELSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>-8.922400000000001</v>
+        <v>-4.9184</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8372</v>
+        <v>-3.053500000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-12.7597</v>
+        <v>-1.8649</v>
       </c>
       <c r="G7" t="n">
-        <v>-16.2959</v>
+        <v>-2.5741</v>
       </c>
       <c r="H7" t="n">
-        <v>-10.7873</v>
+        <v>-3.5703</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.508199999999999</v>
+        <v>0.9959999999999996</v>
       </c>
       <c r="J7" t="n">
-        <v>19.8434</v>
+        <v>10.5382</v>
       </c>
       <c r="K7" t="n">
-        <v>13.2439</v>
+        <v>5.966299999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>6.5994</v>
+        <v>4.5722</v>
       </c>
       <c r="M7" t="n">
-        <v>-36.1395</v>
+        <v>-13.1123</v>
       </c>
       <c r="N7" t="n">
-        <v>-24.0313</v>
+        <v>-9.536300000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-12.1078</v>
+        <v>-3.576</v>
       </c>
       <c r="P7" t="n">
-        <v>15.4406</v>
+        <v>2.8951</v>
       </c>
       <c r="Q7" t="n">
-        <v>-33.9694</v>
+        <v>-12.1595</v>
       </c>
       <c r="R7" t="n">
-        <v>49.4101</v>
+        <v>15.0546</v>
       </c>
       <c r="S7" t="n">
-        <v>5.1349</v>
+        <v>-2.7007</v>
       </c>
       <c r="T7" t="n">
-        <v>3.0784</v>
+        <v>-1.6758</v>
       </c>
       <c r="U7" t="n">
-        <v>2.057</v>
+        <v>-1.0251</v>
       </c>
       <c r="V7" t="n">
-        <v>-13.2025</v>
+        <v>-2.5385</v>
       </c>
       <c r="W7" t="n">
-        <v>14.885</v>
+        <v>0.2437</v>
       </c>
       <c r="X7" t="n">
-        <v>-28.0877</v>
+        <v>-2.7822</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.5473</v>
+        <v>-5.714599999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.597599999999999</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.9498</v>
+        <v>-4.8803</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4128</v>
@@ -1078,13 +1078,13 @@
         <v>17.7566</v>
       </c>
       <c r="S8" t="n">
-        <v>-8.3866</v>
+        <v>-4.5538</v>
       </c>
       <c r="T8" t="n">
-        <v>-5.5098</v>
+        <v>-2.7465</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.8767</v>
+        <v>-1.8071</v>
       </c>
       <c r="V8" t="n">
         <v>2.9895</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. AZANZA TERUEL</t>
+          <t>J. ZHANG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>-10.7319</v>
+        <v>-7.040999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.724</v>
+        <v>-10.1901</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0081</v>
+        <v>3.1496</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.8025</v>
+        <v>-8.052099999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.1126</v>
+        <v>-13.7544</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6897</v>
+        <v>5.702399999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3247</v>
+        <v>6.8485</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.1155</v>
+        <v>-0.3895999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>1.7908</v>
+        <v>7.238700000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.4777</v>
+        <v>-14.9007</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9971</v>
+        <v>-13.3646</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4805</v>
+        <v>-1.5359</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>2.895</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.8251</v>
+        <v>-23.7397</v>
       </c>
       <c r="R9" t="n">
-        <v>6.7551</v>
+        <v>26.6349</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.3022</v>
+        <v>-8.3515</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.574</v>
+        <v>-5.3674</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7284999999999999</v>
+        <v>-2.9842</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.5572</v>
+        <v>6.4679</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>12.0686</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.5572</v>
+        <v>-5.6006</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. BIDAURRE SOLA</t>
+          <t>G. AZANZA TERUEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>-12.2773</v>
+        <v>-9.4496</v>
       </c>
       <c r="E10" t="n">
-        <v>-11.1305</v>
+        <v>-7.9227</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.146699999999999</v>
+        <v>-1.5268</v>
       </c>
       <c r="G10" t="n">
-        <v>16.7691</v>
+        <v>-5.8025</v>
       </c>
       <c r="H10" t="n">
-        <v>5.8578</v>
+        <v>-5.1126</v>
       </c>
       <c r="I10" t="n">
-        <v>10.9118</v>
+        <v>-0.6897</v>
       </c>
       <c r="J10" t="n">
-        <v>38.9392</v>
+        <v>-1.3247</v>
       </c>
       <c r="K10" t="n">
-        <v>21.1218</v>
+        <v>-3.1155</v>
       </c>
       <c r="L10" t="n">
-        <v>17.8174</v>
+        <v>1.7908</v>
       </c>
       <c r="M10" t="n">
-        <v>-22.1701</v>
+        <v>-4.4777</v>
       </c>
       <c r="N10" t="n">
-        <v>-15.2642</v>
+        <v>-1.9971</v>
       </c>
       <c r="O10" t="n">
-        <v>-6.9057</v>
+        <v>-2.4805</v>
       </c>
       <c r="P10" t="n">
-        <v>8.106199999999999</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>-41.4964</v>
+        <v>-4.8251</v>
       </c>
       <c r="R10" t="n">
-        <v>49.6031</v>
+        <v>6.7551</v>
       </c>
       <c r="S10" t="n">
-        <v>-26.2299</v>
+        <v>-2.02</v>
       </c>
       <c r="T10" t="n">
-        <v>-15.7293</v>
+        <v>-1.7728</v>
       </c>
       <c r="U10" t="n">
-        <v>-10.5002</v>
+        <v>-0.2473</v>
       </c>
       <c r="V10" t="n">
-        <v>-10.9231</v>
+        <v>-3.5572</v>
       </c>
       <c r="W10" t="n">
-        <v>7.1567</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-18.0798</v>
+        <v>-3.5572</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.7099</v>
+        <v>-12.2389</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.53</v>
+        <v>-6.653500000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.180099999999999</v>
+        <v>-5.5851</v>
       </c>
       <c r="G11" t="n">
         <v>-8.526999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>15.4404</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3283</v>
+        <v>1.143</v>
       </c>
       <c r="T11" t="n">
-        <v>2.664</v>
+        <v>1.5405</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.9925</v>
+        <v>-0.3977999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-8.714700000000001</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. ZHANG</t>
+          <t>J. MENDIVIL ODERIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.8563</v>
+        <v>-18.3218</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.9113</v>
+        <v>-1.757899999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9450999999999999</v>
+        <v>-16.5639</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.052099999999999</v>
+        <v>-16.2959</v>
       </c>
       <c r="H12" t="n">
-        <v>-13.7544</v>
+        <v>-10.7873</v>
       </c>
       <c r="I12" t="n">
-        <v>5.702399999999999</v>
+        <v>-5.508199999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>6.8485</v>
+        <v>19.8434</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3895999999999999</v>
+        <v>13.2439</v>
       </c>
       <c r="L12" t="n">
-        <v>7.238700000000001</v>
+        <v>6.5994</v>
       </c>
       <c r="M12" t="n">
-        <v>-14.9007</v>
+        <v>-36.1395</v>
       </c>
       <c r="N12" t="n">
-        <v>-13.3646</v>
+        <v>-24.0313</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5359</v>
+        <v>-12.1078</v>
       </c>
       <c r="P12" t="n">
-        <v>2.895</v>
+        <v>15.4406</v>
       </c>
       <c r="Q12" t="n">
-        <v>-23.7397</v>
+        <v>-33.9694</v>
       </c>
       <c r="R12" t="n">
-        <v>26.6349</v>
+        <v>49.4101</v>
       </c>
       <c r="S12" t="n">
-        <v>-16.1669</v>
+        <v>-4.2641</v>
       </c>
       <c r="T12" t="n">
-        <v>-9.0883</v>
+        <v>-2.5164</v>
       </c>
       <c r="U12" t="n">
-        <v>-7.0788</v>
+        <v>-1.7475</v>
       </c>
       <c r="V12" t="n">
-        <v>6.4679</v>
+        <v>-13.2025</v>
       </c>
       <c r="W12" t="n">
-        <v>12.0686</v>
+        <v>14.885</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.6006</v>
+        <v>-28.0877</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. SAVITSKI SAVITSKAIA</t>
+          <t>K. ABU SHAMS SANCHEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.3664</v>
+        <v>-20.6621</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.0906</v>
+        <v>-5.6914</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.276000000000001</v>
+        <v>-14.9706</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.3686</v>
+        <v>-8.862900000000002</v>
       </c>
       <c r="H13" t="n">
-        <v>7.8111</v>
+        <v>-5.0805</v>
       </c>
       <c r="I13" t="n">
-        <v>-13.1799</v>
+        <v>-3.782699999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>30.8951</v>
+        <v>17.7967</v>
       </c>
       <c r="K13" t="n">
-        <v>28.4762</v>
+        <v>12.8382</v>
       </c>
       <c r="L13" t="n">
-        <v>2.418900000000001</v>
+        <v>4.958799999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-36.264</v>
+        <v>-26.6597</v>
       </c>
       <c r="N13" t="n">
-        <v>-20.6654</v>
+        <v>-17.9184</v>
       </c>
       <c r="O13" t="n">
-        <v>-15.599</v>
+        <v>-8.741300000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1929</v>
+        <v>6.368899999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-51.1467</v>
+        <v>-21.6166</v>
       </c>
       <c r="R13" t="n">
-        <v>51.3402</v>
+        <v>27.986</v>
       </c>
       <c r="S13" t="n">
-        <v>5.1557</v>
+        <v>-8.243600000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3092</v>
+        <v>-5.9576</v>
       </c>
       <c r="U13" t="n">
-        <v>6.4648</v>
+        <v>-2.2857</v>
       </c>
       <c r="V13" t="n">
-        <v>-20.3463</v>
+        <v>-9.925000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>6.471</v>
+        <v>4.087</v>
       </c>
       <c r="X13" t="n">
-        <v>-26.8172</v>
+        <v>-14.0118</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. ABU SHAMS SANCHEZ</t>
+          <t>A. SAVITSKI SAVITSKAIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.6337</v>
+        <v>-28.4349</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.971399999999999</v>
+        <v>-17.4809</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.6622</v>
+        <v>-10.9536</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.862900000000002</v>
+        <v>-5.3686</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.0805</v>
+        <v>7.8111</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.782699999999999</v>
+        <v>-13.1799</v>
       </c>
       <c r="J14" t="n">
-        <v>17.7967</v>
+        <v>30.8951</v>
       </c>
       <c r="K14" t="n">
-        <v>12.8382</v>
+        <v>28.4762</v>
       </c>
       <c r="L14" t="n">
-        <v>4.958799999999999</v>
+        <v>2.418900000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-26.6597</v>
+        <v>-36.264</v>
       </c>
       <c r="N14" t="n">
-        <v>-17.9184</v>
+        <v>-20.6654</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.741300000000001</v>
+        <v>-15.599</v>
       </c>
       <c r="P14" t="n">
-        <v>6.368899999999999</v>
+        <v>0.1929</v>
       </c>
       <c r="Q14" t="n">
-        <v>-21.6166</v>
+        <v>-51.1467</v>
       </c>
       <c r="R14" t="n">
-        <v>27.986</v>
+        <v>51.3402</v>
       </c>
       <c r="S14" t="n">
-        <v>-15.2145</v>
+        <v>-2.9126</v>
       </c>
       <c r="T14" t="n">
-        <v>-9.2377</v>
+        <v>-3.6999</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.9767</v>
+        <v>0.7869000000000002</v>
       </c>
       <c r="V14" t="n">
-        <v>-9.925000000000001</v>
+        <v>-20.3463</v>
       </c>
       <c r="W14" t="n">
-        <v>4.087</v>
+        <v>6.471</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.0118</v>
+        <v>-26.8172</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>-34.9451</v>
+        <v>-32.2992</v>
       </c>
       <c r="E15" t="n">
-        <v>-19.3165</v>
+        <v>-18.1959</v>
       </c>
       <c r="F15" t="n">
-        <v>-15.6287</v>
+        <v>-14.103</v>
       </c>
       <c r="G15" t="n">
         <v>-18.2138</v>
@@ -1624,13 +1624,13 @@
         <v>17.1776</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.1907</v>
+        <v>-5.5449</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.447</v>
+        <v>-3.3266</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.7441</v>
+        <v>-2.2186</v>
       </c>
       <c r="V15" t="n">
         <v>-6.2244</v>
@@ -1657,13 +1657,13 @@
         <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>-35.7555</v>
+        <v>-33.828</v>
       </c>
       <c r="E16" t="n">
-        <v>-20.7195</v>
+        <v>-20.2621</v>
       </c>
       <c r="F16" t="n">
-        <v>-15.0363</v>
+        <v>-13.5659</v>
       </c>
       <c r="G16" t="n">
         <v>-23.3571</v>
@@ -1702,13 +1702,13 @@
         <v>35.1276</v>
       </c>
       <c r="S16" t="n">
-        <v>-11.1672</v>
+        <v>-9.2399</v>
       </c>
       <c r="T16" t="n">
-        <v>-5.8811</v>
+        <v>-5.423999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-5.2865</v>
+        <v>-3.816</v>
       </c>
       <c r="V16" t="n">
         <v>-16.2859</v>
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-121.7718</v>
+        <v>-106.1066</v>
       </c>
       <c r="E17" t="n">
-        <v>-27.12810000000001</v>
+        <v>-21.47640000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-94.64399999999999</v>
+        <v>-84.6294</v>
       </c>
       <c r="G17" t="n">
         <v>-66.4807</v>
@@ -1780,13 +1780,13 @@
         <v>435.2323</v>
       </c>
       <c r="S17" t="n">
-        <v>-87.38809999999999</v>
+        <v>-71.7238</v>
       </c>
       <c r="T17" t="n">
-        <v>-56.429</v>
+        <v>-50.7781</v>
       </c>
       <c r="U17" t="n">
-        <v>-30.9594</v>
+        <v>-20.9466</v>
       </c>
       <c r="V17" t="n">
         <v>-27.734</v>
